--- a/롤내전.xlsx
+++ b/롤내전.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\롤내전\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7BBD74-3E06-4367-96FA-C1056FBA7E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70977FB-C07D-429B-AF5E-66195C09DED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3030" yWindow="3030" windowWidth="24810" windowHeight="11970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -4361,7 +4361,7 @@
         <v>14</v>
       </c>
       <c r="K63" s="2">
-        <v>198862</v>
+        <v>19862</v>
       </c>
       <c r="L63" s="2">
         <v>15980</v>
@@ -18672,6 +18672,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -27287,7 +27288,7 @@
         <v>38</v>
       </c>
       <c r="D226" s="1" t="str">
-        <f t="shared" ref="D226:D289" si="4">IF(B226=1,IF(COUNTIFS(A$2:A$1000,A226,C$2:C$1000,C226,E$2:E$1000,"승")&gt;COUNTIFS(A$2:A$1000,A226,C$2:C$1000,C226,E$2:E$1000,"패"),"승","패"),"")</f>
+        <f t="shared" ref="D226:D262" si="4">IF(B226=1,IF(COUNTIFS(A$2:A$1000,A226,C$2:C$1000,C226,E$2:E$1000,"승")&gt;COUNTIFS(A$2:A$1000,A226,C$2:C$1000,C226,E$2:E$1000,"패"),"승","패"),"")</f>
         <v/>
       </c>
       <c r="E226" s="1" t="s">
